--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:31</t>
+          <t>2026-10-14 14:14:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,68 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hri:TableGroupShape/dct:title</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hri:TableGroupShape</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dct:title</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Table group title.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>sh:Literal</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>dash:LiteralViewer</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dash:TextFieldEditor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,23 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>http://schema.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hrishapes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/</t>
         </is>
       </c>
     </row>
@@ -853,7 +870,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#aux-TableGroupShape</t>
+          <t>http://data.health-ri.nl/core/p2/aux-TableGroupShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -991,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:14:50</t>
+          <t>2026-10-14 14:30:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1215,7 +1232,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:TableGroupShape</t>
+          <t>hrishapes:TableGroupShape</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1282,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#TableGroupShape</t>
+          <t>http://data.health-ri.nl/core/p2/TableGroupShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1684,12 +1701,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hri:TableGroupShape/csvw:table</t>
+          <t>hrishapes:TableGroupShape#csvw:table</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hri:TableGroupShape</t>
+          <t>hrishapes:TableGroupShape</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1744,12 +1761,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hri:TableGroupShape/dct:title</t>
+          <t>hrishapes:TableGroupShape#dct:title</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hri:TableGroupShape</t>
+          <t>hrishapes:TableGroupShape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:30:39</t>
+          <t>2026-10-19 15:50:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1733,7 +1733,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#TableShape</t>
+          <t>http://data.health-ri.nl/core/p2/TableShape</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Table group title.</t>
+          <t>Table group title.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1804,9 +1804,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:50:04</t>
+          <t>2026-10-26 13:15:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 13:15:51</t>
+          <t>2026-10-26 16:19:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 16:19:40</t>
+          <t>2026-10-27 15:44:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 15:44:14</t>
+          <t>2026-10-28 09:50:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-tablegroup.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:50:43</t>
+          <t>2026-10-28 11:04:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
